--- a/coaching_forms/012_nervous_system_coaching_call_registration--coaching_forms.xlsx
+++ b/coaching_forms/012_nervous_system_coaching_call_registration--coaching_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'15_minutes'}</t>
+          <t>15_minutes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '15 minutes'}</t>
+          <t>15 minutes</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'30_minutes'}</t>
+          <t>30_minutes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '30 minutes'}</t>
+          <t>30 minutes</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'60_minutes'}</t>
+          <t>60_minutes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '60 minutes'}</t>
+          <t>60 minutes</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'general_wellness'}</t>
+          <t>general_wellness</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'General Wellness'}</t>
+          <t>General Wellness</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'stress_management'}</t>
+          <t>stress_management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Stress Management'}</t>
+          <t>Stress Management</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'anxiety_management'}</t>
+          <t>anxiety_management</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Anxiety Management'}</t>
+          <t>Anxiety Management</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'sleep_coaching'}</t>
+          <t>sleep_coaching</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Sleep Coaching'}</t>
+          <t>Sleep Coaching</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'15_minutes'}</t>
+          <t>15_minutes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '15 minutes'}</t>
+          <t>15 minutes</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'30_minutes'}</t>
+          <t>30_minutes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '30 minutes'}</t>
+          <t>30 minutes</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'60_minutes'}</t>
+          <t>60_minutes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '60 minutes'}</t>
+          <t>60 minutes</t>
         </is>
       </c>
     </row>
